--- a/eMIMO阵面数据帧格式.xlsx
+++ b/eMIMO阵面数据帧格式.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\202409_EMIMO\EMIMO-Software\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WPS_Sync\202409_eMIMO\Software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25C0301-2A63-4176-8F51-93FF19EF2BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4B109C-94E5-41F5-B748-85CE2B7D229E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="43200" windowHeight="23445" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sub Array SPI 32bits Data Frame" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="188">
   <si>
     <t>A15</t>
   </si>
@@ -619,6 +619,9 @@
   <si>
     <t>当sysref_mode=0时，SYSREF_PLSR表示要切换的模式：SYSREF_PLSR=3为连续模式，SYSREF_PLSR=2为Pulser模式，此时SYSREF_PLSR的值会写到SYSREF_MUX寄存器处。sysref_mode=1时表示SYSREF_PLSR_CNT，即LMK04832的Reg318(0x13E)的值，它为00,01,10,11分别表示发送1,2,4,8个脉冲。</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>向LMK04832中写入任意数据　</t>
   </si>
 </sst>
 </file>
@@ -1049,18 +1052,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1072,29 +1063,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1129,7 +1108,31 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1138,11 +1141,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6394,53 +6397,53 @@
       </c>
     </row>
     <row r="18" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33" t="s">
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="26" t="s">
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="29" t="s">
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29" t="s">
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="29"/>
-      <c r="Z18" s="29"/>
-      <c r="AA18" s="29"/>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="29" t="s">
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="AD18" s="29"/>
-      <c r="AE18" s="29"/>
-      <c r="AF18" s="29"/>
-      <c r="AG18" s="29"/>
-      <c r="AH18" s="29"/>
-      <c r="AI18" s="29"/>
-      <c r="AJ18" s="29"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="30"/>
+      <c r="AJ18" s="30"/>
       <c r="AK18" s="16" t="s">
         <v>43</v>
       </c>
@@ -6453,45 +6456,45 @@
       <c r="AN18" s="22"/>
     </row>
     <row r="19" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="26" t="s">
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="29" t="s">
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29" t="s">
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
-      <c r="Y19" s="29"/>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="29"/>
-      <c r="AB19" s="29"/>
-      <c r="AC19" s="29"/>
-      <c r="AD19" s="29"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="29"/>
-      <c r="AG19" s="29"/>
-      <c r="AH19" s="29"/>
-      <c r="AI19" s="29"/>
-      <c r="AJ19" s="29"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+      <c r="AA19" s="30"/>
+      <c r="AB19" s="30"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="30"/>
       <c r="AK19" s="16" t="s">
         <v>47</v>
       </c>
@@ -6506,51 +6509,51 @@
       </c>
     </row>
     <row r="20" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33" t="s">
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="29" t="s">
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="30" t="s">
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="32"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
+      <c r="X20" s="27"/>
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="28"/>
       <c r="AA20" s="11" t="s">
         <v>53</v>
       </c>
       <c r="AB20" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AC20" s="29" t="s">
+      <c r="AC20" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
-      <c r="AG20" s="29"/>
-      <c r="AH20" s="29"/>
-      <c r="AI20" s="29"/>
-      <c r="AJ20" s="29"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="30"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="30"/>
+      <c r="AJ20" s="30"/>
       <c r="AK20" s="16" t="s">
         <v>56</v>
       </c>
@@ -6563,49 +6566,49 @@
       <c r="AN20" s="22"/>
     </row>
     <row r="21" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="29" t="s">
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="26" t="s">
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
-      <c r="X21" s="27"/>
-      <c r="Y21" s="27"/>
-      <c r="Z21" s="27"/>
-      <c r="AA21" s="28"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="33"/>
       <c r="AB21" s="11" t="s">
         <v>54</v>
       </c>
       <c r="AC21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AD21" s="30" t="s">
+      <c r="AD21" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="AE21" s="31"/>
-      <c r="AF21" s="31"/>
-      <c r="AG21" s="31"/>
-      <c r="AH21" s="31"/>
-      <c r="AI21" s="31"/>
-      <c r="AJ21" s="32"/>
+      <c r="AE21" s="27"/>
+      <c r="AF21" s="27"/>
+      <c r="AG21" s="27"/>
+      <c r="AH21" s="27"/>
+      <c r="AI21" s="27"/>
+      <c r="AJ21" s="28"/>
       <c r="AK21" s="9" t="s">
         <v>61</v>
       </c>
@@ -6618,51 +6621,51 @@
       <c r="AN21" s="22"/>
     </row>
     <row r="22" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33" t="s">
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="29" t="s">
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="30" t="s">
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="32"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="27"/>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="28"/>
       <c r="AA22" s="11" t="s">
         <v>66</v>
       </c>
       <c r="AB22" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AC22" s="30" t="s">
+      <c r="AC22" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
-      <c r="AG22" s="31"/>
-      <c r="AH22" s="31"/>
-      <c r="AI22" s="31"/>
-      <c r="AJ22" s="32"/>
+      <c r="AD22" s="27"/>
+      <c r="AE22" s="27"/>
+      <c r="AF22" s="27"/>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="27"/>
+      <c r="AI22" s="27"/>
+      <c r="AJ22" s="28"/>
       <c r="AK22" s="9" t="s">
         <v>68</v>
       </c>
@@ -6675,45 +6678,45 @@
       <c r="AN22" s="22"/>
     </row>
     <row r="23" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="26" t="s">
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="29" t="s">
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="30" t="s">
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="31"/>
-      <c r="AF23" s="31"/>
-      <c r="AG23" s="31"/>
-      <c r="AH23" s="31"/>
-      <c r="AI23" s="31"/>
-      <c r="AJ23" s="32"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="27"/>
+      <c r="AA23" s="27"/>
+      <c r="AB23" s="27"/>
+      <c r="AC23" s="27"/>
+      <c r="AD23" s="27"/>
+      <c r="AE23" s="27"/>
+      <c r="AF23" s="27"/>
+      <c r="AG23" s="27"/>
+      <c r="AH23" s="27"/>
+      <c r="AI23" s="27"/>
+      <c r="AJ23" s="28"/>
       <c r="AK23" s="9" t="s">
         <v>72</v>
       </c>
@@ -6726,45 +6729,45 @@
       <c r="AN23" s="22"/>
     </row>
     <row r="24" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="26" t="s">
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="29" t="s">
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="30" t="s">
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="31"/>
-      <c r="AE24" s="31"/>
-      <c r="AF24" s="31"/>
-      <c r="AG24" s="31"/>
-      <c r="AH24" s="31"/>
-      <c r="AI24" s="31"/>
-      <c r="AJ24" s="32"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="27"/>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="27"/>
+      <c r="Z24" s="27"/>
+      <c r="AA24" s="27"/>
+      <c r="AB24" s="27"/>
+      <c r="AC24" s="27"/>
+      <c r="AD24" s="27"/>
+      <c r="AE24" s="27"/>
+      <c r="AF24" s="27"/>
+      <c r="AG24" s="27"/>
+      <c r="AH24" s="27"/>
+      <c r="AI24" s="27"/>
+      <c r="AJ24" s="28"/>
       <c r="AK24" s="9" t="s">
         <v>75</v>
       </c>
@@ -6777,49 +6780,49 @@
       <c r="AN24" s="22"/>
     </row>
     <row r="25" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="26" t="s">
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="29" t="s">
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="30" t="s">
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="29" t="s">
+      <c r="V25" s="27"/>
+      <c r="W25" s="27"/>
+      <c r="X25" s="27"/>
+      <c r="Y25" s="27"/>
+      <c r="Z25" s="27"/>
+      <c r="AA25" s="27"/>
+      <c r="AB25" s="27"/>
+      <c r="AC25" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AD25" s="29"/>
-      <c r="AE25" s="29"/>
-      <c r="AF25" s="29"/>
-      <c r="AG25" s="30" t="s">
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="AH25" s="31"/>
-      <c r="AI25" s="31"/>
-      <c r="AJ25" s="32"/>
+      <c r="AH25" s="27"/>
+      <c r="AI25" s="27"/>
+      <c r="AJ25" s="28"/>
       <c r="AK25" s="9" t="s">
         <v>78</v>
       </c>
@@ -6832,49 +6835,49 @@
       <c r="AN25" s="22"/>
     </row>
     <row r="26" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33" t="s">
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="29" t="s">
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="30" t="s">
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="32"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="28"/>
       <c r="AB26" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="AC26" s="29" t="s">
+      <c r="AC26" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="29"/>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="29"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
       <c r="AK26" s="16" t="s">
         <v>82</v>
       </c>
@@ -6887,49 +6890,49 @@
       <c r="AN26" s="22"/>
     </row>
     <row r="27" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="29" t="s">
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="30" t="s">
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="32"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="28"/>
       <c r="AB27" s="11" t="s">
         <v>54</v>
       </c>
       <c r="AC27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AD27" s="30" t="s">
+      <c r="AD27" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="32"/>
+      <c r="AE27" s="27"/>
+      <c r="AF27" s="27"/>
+      <c r="AG27" s="27"/>
+      <c r="AH27" s="27"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="28"/>
       <c r="AK27" s="9" t="s">
         <v>85</v>
       </c>
@@ -6942,53 +6945,53 @@
       <c r="AN27" s="22"/>
     </row>
     <row r="28" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33" t="s">
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33" t="s">
+      <c r="N28" s="29"/>
+      <c r="O28" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="29" t="s">
+      <c r="P28" s="29"/>
+      <c r="Q28" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="30" t="s">
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="32"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="28"/>
       <c r="AB28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AC28" s="29" t="s">
+      <c r="AC28" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="30" t="s">
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="32"/>
+      <c r="AF28" s="27"/>
+      <c r="AG28" s="27"/>
+      <c r="AH28" s="27"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="28"/>
       <c r="AK28" s="9" t="s">
         <v>90</v>
       </c>
@@ -7594,6 +7597,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="U18:AB18"/>
+    <mergeCell ref="AC18:AJ18"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="U19:AJ19"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="U20:Z20"/>
+    <mergeCell ref="AC20:AJ20"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="U21:AA21"/>
+    <mergeCell ref="AD21:AJ21"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="U22:Z22"/>
+    <mergeCell ref="AC22:AJ22"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="U23:AJ23"/>
+    <mergeCell ref="AD27:AJ27"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:AJ24"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:AB25"/>
+    <mergeCell ref="AC25:AF25"/>
+    <mergeCell ref="AG25:AJ25"/>
     <mergeCell ref="AE28:AJ28"/>
     <mergeCell ref="D18:D28"/>
     <mergeCell ref="E18:H28"/>
@@ -7610,35 +7642,6 @@
     <mergeCell ref="AC26:AJ26"/>
     <mergeCell ref="Q27:T27"/>
     <mergeCell ref="U27:AA27"/>
-    <mergeCell ref="AD27:AJ27"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:T24"/>
-    <mergeCell ref="U24:AJ24"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="Q25:T25"/>
-    <mergeCell ref="U25:AB25"/>
-    <mergeCell ref="AC25:AF25"/>
-    <mergeCell ref="AG25:AJ25"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="Q22:T22"/>
-    <mergeCell ref="U22:Z22"/>
-    <mergeCell ref="AC22:AJ22"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="Q23:T23"/>
-    <mergeCell ref="U23:AJ23"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="U20:Z20"/>
-    <mergeCell ref="AC20:AJ20"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="U21:AA21"/>
-    <mergeCell ref="AD21:AJ21"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="U18:AB18"/>
-    <mergeCell ref="AC18:AJ18"/>
-    <mergeCell ref="M19:P19"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="U19:AJ19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7670,74 +7673,74 @@
       <c r="F21" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G21" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="35" t="s">
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="P21" s="36" t="s">
+      <c r="P21" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="Q21" s="36" t="s">
+      <c r="Q21" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="R21" s="36"/>
-      <c r="S21" s="36"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="35" t="s">
+      <c r="R21" s="51"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="51"/>
+      <c r="V21" s="52"/>
+      <c r="W21" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="36"/>
-      <c r="Z21" s="36"/>
-      <c r="AA21" s="36"/>
-      <c r="AB21" s="36"/>
-      <c r="AC21" s="36"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="35" t="s">
+      <c r="X21" s="51"/>
+      <c r="Y21" s="51"/>
+      <c r="Z21" s="51"/>
+      <c r="AA21" s="51"/>
+      <c r="AB21" s="51"/>
+      <c r="AC21" s="51"/>
+      <c r="AD21" s="52"/>
+      <c r="AE21" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="AF21" s="36"/>
-      <c r="AG21" s="36"/>
-      <c r="AH21" s="36"/>
-      <c r="AI21" s="36"/>
-      <c r="AJ21" s="36"/>
-      <c r="AK21" s="36"/>
-      <c r="AL21" s="37"/>
+      <c r="AF21" s="51"/>
+      <c r="AG21" s="51"/>
+      <c r="AH21" s="51"/>
+      <c r="AI21" s="51"/>
+      <c r="AJ21" s="51"/>
+      <c r="AK21" s="51"/>
+      <c r="AL21" s="52"/>
       <c r="AM21" s="1" t="s">
         <v>99</v>
       </c>
       <c r="AN21" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AO21" s="42" t="s">
+      <c r="AO21" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="AP21" s="42" t="s">
+      <c r="AP21" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="AQ21" s="42" t="s">
+      <c r="AQ21" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="AR21" s="43" t="s">
+      <c r="AR21" s="35" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="5:44" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="34"/>
+      <c r="F22" s="45"/>
       <c r="G22" s="3" t="s">
         <v>102</v>
       </c>
@@ -7834,56 +7837,56 @@
       <c r="AL22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AM22" s="34" t="s">
+      <c r="AM22" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="AN22" s="53"/>
-      <c r="AO22" s="42"/>
-      <c r="AP22" s="42"/>
-      <c r="AQ22" s="42"/>
-      <c r="AR22" s="43"/>
+      <c r="AN22" s="46"/>
+      <c r="AO22" s="34"/>
+      <c r="AP22" s="34"/>
+      <c r="AQ22" s="34"/>
+      <c r="AR22" s="35"/>
     </row>
     <row r="23" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="F23" s="38" t="s">
+      <c r="F23" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
-      <c r="AG23" s="29"/>
-      <c r="AH23" s="29"/>
-      <c r="AI23" s="29"/>
-      <c r="AJ23" s="29"/>
-      <c r="AK23" s="29"/>
-      <c r="AL23" s="29"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
+      <c r="AG23" s="30"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="30"/>
       <c r="AM23" s="4" t="s">
         <v>122</v>
       </c>
@@ -7901,56 +7904,56 @@
       </c>
     </row>
     <row r="24" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="44" t="s">
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="44" t="s">
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="30" t="s">
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="30" t="s">
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="29" t="s">
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="28"/>
+      <c r="W24" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="X24" s="29"/>
-      <c r="Y24" s="29"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="29"/>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
-      <c r="AE24" s="29"/>
-      <c r="AF24" s="29"/>
-      <c r="AG24" s="29"/>
-      <c r="AH24" s="29"/>
-      <c r="AI24" s="29"/>
-      <c r="AJ24" s="29"/>
-      <c r="AK24" s="29"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
       <c r="AL24" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AM24" s="39" t="s">
+      <c r="AM24" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="AN24" s="39" t="s">
+      <c r="AN24" s="47" t="s">
         <v>122</v>
       </c>
       <c r="AO24" s="16" t="s">
@@ -7964,48 +7967,48 @@
       </c>
     </row>
     <row r="25" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="49"/>
-      <c r="O25" s="30" t="s">
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="30" t="s">
+      <c r="P25" s="27"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="32"/>
-      <c r="W25" s="30" t="s">
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="28"/>
+      <c r="W25" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="31"/>
-      <c r="AF25" s="31"/>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="31"/>
-      <c r="AI25" s="31"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="31"/>
-      <c r="AL25" s="32"/>
-      <c r="AM25" s="40"/>
-      <c r="AN25" s="40"/>
+      <c r="X25" s="27"/>
+      <c r="Y25" s="27"/>
+      <c r="Z25" s="27"/>
+      <c r="AA25" s="27"/>
+      <c r="AB25" s="27"/>
+      <c r="AC25" s="27"/>
+      <c r="AD25" s="27"/>
+      <c r="AE25" s="27"/>
+      <c r="AF25" s="27"/>
+      <c r="AG25" s="27"/>
+      <c r="AH25" s="27"/>
+      <c r="AI25" s="27"/>
+      <c r="AJ25" s="27"/>
+      <c r="AK25" s="27"/>
+      <c r="AL25" s="28"/>
+      <c r="AM25" s="48"/>
+      <c r="AN25" s="48"/>
       <c r="AO25" s="16" t="s">
         <v>130</v>
       </c>
@@ -8017,48 +8020,48 @@
       </c>
     </row>
     <row r="26" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="30" t="s">
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="30" t="s">
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="30" t="s">
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="32"/>
-      <c r="AM26" s="40"/>
-      <c r="AN26" s="40"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="27"/>
+      <c r="AB26" s="27"/>
+      <c r="AC26" s="27"/>
+      <c r="AD26" s="27"/>
+      <c r="AE26" s="27"/>
+      <c r="AF26" s="27"/>
+      <c r="AG26" s="27"/>
+      <c r="AH26" s="27"/>
+      <c r="AI26" s="27"/>
+      <c r="AJ26" s="27"/>
+      <c r="AK26" s="27"/>
+      <c r="AL26" s="28"/>
+      <c r="AM26" s="48"/>
+      <c r="AN26" s="48"/>
       <c r="AO26" s="16" t="s">
         <v>133</v>
       </c>
@@ -8073,52 +8076,52 @@
       </c>
     </row>
     <row r="27" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="49"/>
-      <c r="O27" s="30" t="s">
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="30" t="s">
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="30" t="s">
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="29" t="s">
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
+      <c r="AD27" s="28"/>
+      <c r="AE27" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AF27" s="29"/>
-      <c r="AG27" s="29"/>
-      <c r="AH27" s="29"/>
-      <c r="AI27" s="29" t="s">
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="AJ27" s="29"/>
-      <c r="AK27" s="29"/>
-      <c r="AL27" s="29"/>
-      <c r="AM27" s="40"/>
-      <c r="AN27" s="40"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
+      <c r="AM27" s="48"/>
+      <c r="AN27" s="48"/>
       <c r="AO27" s="16" t="s">
         <v>137</v>
       </c>
@@ -8130,52 +8133,52 @@
       </c>
     </row>
     <row r="28" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="30" t="s">
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="30" t="s">
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="30" t="s">
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="32"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="28"/>
       <c r="AD28" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="AE28" s="30" t="s">
+      <c r="AE28" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="40"/>
-      <c r="AN28" s="40"/>
+      <c r="AF28" s="27"/>
+      <c r="AG28" s="27"/>
+      <c r="AH28" s="27"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="27"/>
+      <c r="AK28" s="27"/>
+      <c r="AL28" s="28"/>
+      <c r="AM28" s="48"/>
+      <c r="AN28" s="48"/>
       <c r="AO28" s="16" t="s">
         <v>142</v>
       </c>
@@ -8187,54 +8190,54 @@
       </c>
     </row>
     <row r="29" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="30" t="s">
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="30" t="s">
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="30" t="s">
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="32"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="28"/>
       <c r="AD29" s="5" t="s">
         <v>141</v>
       </c>
       <c r="AE29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AF29" s="30" t="s">
+      <c r="AF29" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="AG29" s="31"/>
-      <c r="AH29" s="31"/>
-      <c r="AI29" s="31"/>
-      <c r="AJ29" s="31"/>
-      <c r="AK29" s="31"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="41"/>
-      <c r="AN29" s="41"/>
+      <c r="AG29" s="27"/>
+      <c r="AH29" s="27"/>
+      <c r="AI29" s="27"/>
+      <c r="AJ29" s="27"/>
+      <c r="AK29" s="27"/>
+      <c r="AL29" s="28"/>
+      <c r="AM29" s="49"/>
+      <c r="AN29" s="49"/>
       <c r="AO29" s="16" t="s">
         <v>144</v>
       </c>
@@ -8247,6 +8250,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="S24:V24"/>
+    <mergeCell ref="W24:AK24"/>
+    <mergeCell ref="G21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="AE21:AL21"/>
+    <mergeCell ref="E23:E29"/>
+    <mergeCell ref="F23:F29"/>
+    <mergeCell ref="AM24:AM29"/>
+    <mergeCell ref="AN24:AN29"/>
+    <mergeCell ref="AO21:AO22"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="S28:V28"/>
+    <mergeCell ref="W28:AC28"/>
+    <mergeCell ref="AE28:AL28"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="S29:V29"/>
+    <mergeCell ref="W29:AC29"/>
+    <mergeCell ref="AF29:AL29"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="S27:V27"/>
+    <mergeCell ref="W27:AD27"/>
     <mergeCell ref="AP21:AP22"/>
     <mergeCell ref="AQ21:AQ22"/>
     <mergeCell ref="AR21:AR22"/>
@@ -8263,29 +8289,6 @@
     <mergeCell ref="AM22:AN22"/>
     <mergeCell ref="G23:AL23"/>
     <mergeCell ref="O24:R24"/>
-    <mergeCell ref="AM24:AM29"/>
-    <mergeCell ref="AN24:AN29"/>
-    <mergeCell ref="AO21:AO22"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="S28:V28"/>
-    <mergeCell ref="W28:AC28"/>
-    <mergeCell ref="AE28:AL28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="S29:V29"/>
-    <mergeCell ref="W29:AC29"/>
-    <mergeCell ref="AF29:AL29"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="S27:V27"/>
-    <mergeCell ref="W27:AD27"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="S24:V24"/>
-    <mergeCell ref="W24:AK24"/>
-    <mergeCell ref="G21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="AE21:AL21"/>
-    <mergeCell ref="E23:E29"/>
-    <mergeCell ref="F23:F29"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8312,65 +8315,65 @@
       <c r="D13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="35" t="s">
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="N13" s="36" t="s">
+      <c r="N13" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="36" t="s">
+      <c r="O13" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="35" t="s">
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="35" t="s">
+      <c r="V13" s="51"/>
+      <c r="W13" s="51"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="51"/>
+      <c r="Z13" s="51"/>
+      <c r="AA13" s="51"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="AD13" s="36"/>
-      <c r="AE13" s="36"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="36"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="37"/>
+      <c r="AD13" s="51"/>
+      <c r="AE13" s="51"/>
+      <c r="AF13" s="51"/>
+      <c r="AG13" s="51"/>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="51"/>
+      <c r="AJ13" s="52"/>
       <c r="AK13" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="AL13" s="42" t="s">
+      <c r="AL13" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="AM13" s="42" t="s">
+      <c r="AM13" s="34" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="3:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="45"/>
       <c r="E14" s="3" t="s">
         <v>102</v>
       </c>
@@ -8468,66 +8471,66 @@
         <v>31</v>
       </c>
       <c r="AK14" s="55"/>
-      <c r="AL14" s="42"/>
-      <c r="AM14" s="42"/>
+      <c r="AL14" s="34"/>
+      <c r="AM14" s="34"/>
     </row>
     <row r="15" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="32" t="s">
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="29"/>
-      <c r="K15" s="26" t="s">
+      <c r="J15" s="30"/>
+      <c r="K15" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="L15" s="28"/>
-      <c r="M15" s="26" t="s">
+      <c r="L15" s="33"/>
+      <c r="M15" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="29" t="s">
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="30" t="s">
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V15" s="31"/>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="32"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="28"/>
       <c r="AA15" s="11" t="s">
         <v>66</v>
       </c>
       <c r="AB15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AC15" s="30" t="s">
+      <c r="AC15" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="AD15" s="31"/>
-      <c r="AE15" s="31"/>
-      <c r="AF15" s="31"/>
-      <c r="AG15" s="31"/>
-      <c r="AH15" s="31"/>
-      <c r="AI15" s="31"/>
-      <c r="AJ15" s="32"/>
+      <c r="AD15" s="27"/>
+      <c r="AE15" s="27"/>
+      <c r="AF15" s="27"/>
+      <c r="AG15" s="27"/>
+      <c r="AH15" s="27"/>
+      <c r="AI15" s="27"/>
+      <c r="AJ15" s="28"/>
       <c r="AK15" s="9" t="s">
         <v>147</v>
       </c>
@@ -8539,48 +8542,48 @@
       </c>
     </row>
     <row r="16" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="27" t="s">
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="26" t="s">
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29" t="s">
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="30" t="s">
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31"/>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
-      <c r="AF16" s="31"/>
-      <c r="AG16" s="31"/>
-      <c r="AH16" s="31"/>
-      <c r="AI16" s="31"/>
-      <c r="AJ16" s="32"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
+      <c r="AG16" s="27"/>
+      <c r="AH16" s="27"/>
+      <c r="AI16" s="27"/>
+      <c r="AJ16" s="28"/>
       <c r="AK16" s="9" t="s">
         <v>75</v>
       </c>
@@ -8592,50 +8595,50 @@
       </c>
     </row>
     <row r="17" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="27" t="s">
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="26" t="s">
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="29" t="s">
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="30" t="s">
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31"/>
-      <c r="AC17" s="31"/>
-      <c r="AD17" s="31"/>
-      <c r="AE17" s="31"/>
-      <c r="AF17" s="32"/>
-      <c r="AG17" s="30" t="s">
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="27"/>
+      <c r="AC17" s="27"/>
+      <c r="AD17" s="27"/>
+      <c r="AE17" s="27"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="AH17" s="31"/>
-      <c r="AI17" s="31"/>
-      <c r="AJ17" s="32"/>
+      <c r="AH17" s="27"/>
+      <c r="AI17" s="27"/>
+      <c r="AJ17" s="28"/>
       <c r="AK17" s="9" t="s">
         <v>78</v>
       </c>
@@ -8647,56 +8650,56 @@
       </c>
     </row>
     <row r="18" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="32" t="s">
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="29"/>
-      <c r="K18" s="26" t="s">
+      <c r="J18" s="30"/>
+      <c r="K18" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="L18" s="28"/>
-      <c r="M18" s="33" t="s">
+      <c r="L18" s="33"/>
+      <c r="M18" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="29" t="s">
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="30" t="s">
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V18" s="31"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="29" t="s">
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="28"/>
+      <c r="AA18" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="29" t="s">
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AD18" s="29"/>
-      <c r="AE18" s="30" t="s">
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="AF18" s="31"/>
-      <c r="AG18" s="31"/>
-      <c r="AH18" s="31"/>
-      <c r="AI18" s="31"/>
-      <c r="AJ18" s="32"/>
+      <c r="AF18" s="27"/>
+      <c r="AG18" s="27"/>
+      <c r="AH18" s="27"/>
+      <c r="AI18" s="27"/>
+      <c r="AJ18" s="28"/>
       <c r="AK18" s="9" t="s">
         <v>154</v>
       </c>
@@ -8708,55 +8711,55 @@
       </c>
     </row>
     <row r="19" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="32" t="s">
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="29"/>
-      <c r="K19" s="26" t="s">
+      <c r="J19" s="30"/>
+      <c r="K19" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="L19" s="28"/>
+      <c r="L19" s="33"/>
       <c r="M19" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="26" t="s">
+      <c r="N19" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="O19" s="27"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="29" t="s">
+      <c r="O19" s="32"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="30" t="s">
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="31"/>
-      <c r="AA19" s="32"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="28"/>
       <c r="AB19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AC19" s="29" t="s">
+      <c r="AC19" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AD19" s="29"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="29"/>
-      <c r="AG19" s="29"/>
-      <c r="AH19" s="29"/>
-      <c r="AI19" s="29"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
       <c r="AJ19" s="12" t="s">
         <v>160</v>
       </c>
@@ -8772,6 +8775,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="E13:L13"/>
+    <mergeCell ref="M13:T13"/>
+    <mergeCell ref="U13:AB13"/>
+    <mergeCell ref="AC13:AJ13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="AG17:AJ17"/>
+    <mergeCell ref="AC15:AJ15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="U16:AJ16"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="U15:Z15"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="U17:AF17"/>
     <mergeCell ref="C15:C19"/>
     <mergeCell ref="D15:D19"/>
     <mergeCell ref="AK13:AK14"/>
@@ -8788,30 +8815,6 @@
     <mergeCell ref="U19:AA19"/>
     <mergeCell ref="AC19:AI19"/>
     <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="Q17:T17"/>
-    <mergeCell ref="U17:AF17"/>
-    <mergeCell ref="AG17:AJ17"/>
-    <mergeCell ref="AC15:AJ15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:P16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="U16:AJ16"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U15:Z15"/>
-    <mergeCell ref="E13:L13"/>
-    <mergeCell ref="M13:T13"/>
-    <mergeCell ref="U13:AB13"/>
-    <mergeCell ref="AC13:AJ13"/>
-    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8838,65 +8841,65 @@
       <c r="D13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="35" t="s">
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="N13" s="36" t="s">
+      <c r="N13" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="36" t="s">
+      <c r="O13" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="35" t="s">
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="35" t="s">
+      <c r="V13" s="51"/>
+      <c r="W13" s="51"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="51"/>
+      <c r="Z13" s="51"/>
+      <c r="AA13" s="51"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="AD13" s="36"/>
-      <c r="AE13" s="36"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="36"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="37"/>
+      <c r="AD13" s="51"/>
+      <c r="AE13" s="51"/>
+      <c r="AF13" s="51"/>
+      <c r="AG13" s="51"/>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="51"/>
+      <c r="AJ13" s="52"/>
       <c r="AK13" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="AL13" s="42" t="s">
+      <c r="AL13" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="AM13" s="42" t="s">
+      <c r="AM13" s="34" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="3:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="45"/>
       <c r="E14" s="3" t="s">
         <v>102</v>
       </c>
@@ -8994,62 +8997,62 @@
         <v>31</v>
       </c>
       <c r="AK14" s="55"/>
-      <c r="AL14" s="42"/>
-      <c r="AM14" s="42"/>
+      <c r="AL14" s="34"/>
+      <c r="AM14" s="34"/>
     </row>
     <row r="15" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="26" t="s">
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="29" t="s">
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="30" t="s">
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V15" s="31"/>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="32"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="28"/>
       <c r="AA15" s="11" t="s">
         <v>66</v>
       </c>
       <c r="AB15" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AC15" s="30" t="s">
+      <c r="AC15" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="AD15" s="31"/>
-      <c r="AE15" s="31"/>
-      <c r="AF15" s="31"/>
-      <c r="AG15" s="31"/>
-      <c r="AH15" s="31"/>
-      <c r="AI15" s="31"/>
-      <c r="AJ15" s="32"/>
+      <c r="AD15" s="27"/>
+      <c r="AE15" s="27"/>
+      <c r="AF15" s="27"/>
+      <c r="AG15" s="27"/>
+      <c r="AH15" s="27"/>
+      <c r="AI15" s="27"/>
+      <c r="AJ15" s="28"/>
       <c r="AK15" s="9" t="s">
         <v>147</v>
       </c>
@@ -9061,46 +9064,46 @@
       </c>
     </row>
     <row r="16" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="26" t="s">
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="29" t="s">
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="30" t="s">
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31"/>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
-      <c r="AF16" s="31"/>
-      <c r="AG16" s="31"/>
-      <c r="AH16" s="31"/>
-      <c r="AI16" s="31"/>
-      <c r="AJ16" s="32"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
+      <c r="AG16" s="27"/>
+      <c r="AH16" s="27"/>
+      <c r="AI16" s="27"/>
+      <c r="AJ16" s="28"/>
       <c r="AK16" s="9" t="s">
         <v>75</v>
       </c>
@@ -9112,48 +9115,48 @@
       </c>
     </row>
     <row r="17" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="26" t="s">
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="29" t="s">
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="30" t="s">
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="29" t="s">
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="AD17" s="29"/>
-      <c r="AE17" s="29"/>
-      <c r="AF17" s="29"/>
-      <c r="AG17" s="29"/>
-      <c r="AH17" s="29"/>
-      <c r="AI17" s="29"/>
-      <c r="AJ17" s="29"/>
+      <c r="AD17" s="30"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="30"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="30"/>
+      <c r="AJ17" s="30"/>
       <c r="AK17" s="9" t="s">
         <v>78</v>
       </c>
@@ -9165,54 +9168,54 @@
       </c>
     </row>
     <row r="18" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="49"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="41"/>
       <c r="M18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="26" t="s">
+      <c r="N18" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="O18" s="27"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="29" t="s">
+      <c r="O18" s="32"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="30" t="s">
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V18" s="31"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="29" t="s">
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="28"/>
+      <c r="AA18" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="29" t="s">
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AD18" s="29"/>
-      <c r="AE18" s="30" t="s">
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="AF18" s="31"/>
-      <c r="AG18" s="31"/>
-      <c r="AH18" s="31"/>
-      <c r="AI18" s="31"/>
-      <c r="AJ18" s="32"/>
+      <c r="AF18" s="27"/>
+      <c r="AG18" s="27"/>
+      <c r="AH18" s="27"/>
+      <c r="AI18" s="27"/>
+      <c r="AJ18" s="28"/>
       <c r="AK18" s="9" t="s">
         <v>154</v>
       </c>
@@ -9224,51 +9227,51 @@
       </c>
     </row>
     <row r="19" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="33" t="s">
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="33"/>
-      <c r="O19" s="27" t="s">
+      <c r="N19" s="29"/>
+      <c r="O19" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="29" t="s">
+      <c r="P19" s="33"/>
+      <c r="Q19" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="30" t="s">
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="31"/>
-      <c r="AA19" s="32"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="28"/>
       <c r="AB19" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AC19" s="29" t="s">
+      <c r="AC19" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AD19" s="29"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="29"/>
-      <c r="AG19" s="29"/>
-      <c r="AH19" s="29"/>
-      <c r="AI19" s="29"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
       <c r="AJ19" s="12" t="s">
         <v>160</v>
       </c>
@@ -9284,6 +9287,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="E13:L13"/>
+    <mergeCell ref="M13:T13"/>
+    <mergeCell ref="U13:AB13"/>
+    <mergeCell ref="AC13:AJ13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="M15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="U15:Z15"/>
+    <mergeCell ref="AC15:AJ15"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="U16:AJ16"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AE18:AJ18"/>
     <mergeCell ref="C15:C19"/>
     <mergeCell ref="D15:D19"/>
     <mergeCell ref="AK13:AK14"/>
@@ -9300,23 +9320,6 @@
     <mergeCell ref="U17:AB17"/>
     <mergeCell ref="AC17:AJ17"/>
     <mergeCell ref="N18:P18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="AE18:AJ18"/>
-    <mergeCell ref="M15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U15:Z15"/>
-    <mergeCell ref="AC15:AJ15"/>
-    <mergeCell ref="M16:P16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="U16:AJ16"/>
-    <mergeCell ref="E13:L13"/>
-    <mergeCell ref="M13:T13"/>
-    <mergeCell ref="U13:AB13"/>
-    <mergeCell ref="AC13:AJ13"/>
-    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9343,50 +9346,50 @@
       <c r="D9" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="35" t="s">
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="N9" s="36" t="s">
+      <c r="N9" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="O9" s="36" t="s">
+      <c r="O9" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="35" t="s">
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="35" t="s">
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="51"/>
+      <c r="AA9" s="51"/>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="AD9" s="36"/>
-      <c r="AE9" s="36"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="36"/>
-      <c r="AH9" s="36"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="37"/>
+      <c r="AD9" s="51"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="51"/>
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="51"/>
+      <c r="AI9" s="51"/>
+      <c r="AJ9" s="52"/>
       <c r="AK9" s="1" t="s">
         <v>99</v>
       </c>
@@ -9396,18 +9399,18 @@
       <c r="AM9" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="AN9" s="42" t="s">
+      <c r="AN9" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="AO9" s="42" t="s">
+      <c r="AO9" s="34" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="3:41" x14ac:dyDescent="0.2">
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="45"/>
       <c r="E10" s="3" t="s">
         <v>102</v>
       </c>
@@ -9504,67 +9507,67 @@
       <c r="AJ10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AK10" s="34" t="s">
+      <c r="AK10" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="AL10" s="53"/>
+      <c r="AL10" s="46"/>
       <c r="AM10" s="55"/>
-      <c r="AN10" s="42"/>
-      <c r="AO10" s="42"/>
+      <c r="AN10" s="34"/>
+      <c r="AO10" s="34"/>
     </row>
     <row r="11" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="26" t="s">
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="29" t="s">
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="57" t="s">
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="29"/>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="29"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="30"/>
       <c r="AJ11" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="AK11" s="38" t="s">
+      <c r="AK11" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="AL11" s="38" t="s">
+      <c r="AL11" s="53" t="s">
         <v>123</v>
       </c>
       <c r="AM11" s="9" t="s">
@@ -9578,48 +9581,48 @@
       </c>
     </row>
     <row r="12" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="26" t="s">
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="29" t="s">
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
       <c r="U12" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="V12" s="31"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
-      <c r="AA12" s="31"/>
-      <c r="AB12" s="31"/>
-      <c r="AC12" s="31"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="31"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="31"/>
-      <c r="AI12" s="31"/>
-      <c r="AJ12" s="32"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="27"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="27"/>
+      <c r="AF12" s="27"/>
+      <c r="AG12" s="27"/>
+      <c r="AH12" s="27"/>
+      <c r="AI12" s="27"/>
+      <c r="AJ12" s="28"/>
+      <c r="AK12" s="53"/>
+      <c r="AL12" s="53"/>
       <c r="AM12" s="24" t="s">
         <v>179</v>
       </c>
@@ -9631,50 +9634,50 @@
       </c>
     </row>
     <row r="13" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="56" t="s">
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="57" t="s">
         <v>176</v>
       </c>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="57" t="s">
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="56" t="s">
         <v>175</v>
       </c>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
       <c r="U13" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="31"/>
-      <c r="AC13" s="31"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="31"/>
-      <c r="AF13" s="31"/>
-      <c r="AG13" s="31"/>
-      <c r="AH13" s="32"/>
-      <c r="AI13" s="57" t="s">
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="27"/>
+      <c r="AG13" s="27"/>
+      <c r="AH13" s="28"/>
+      <c r="AI13" s="56" t="s">
         <v>184</v>
       </c>
-      <c r="AJ13" s="29"/>
-      <c r="AK13" s="38"/>
-      <c r="AL13" s="38"/>
+      <c r="AJ13" s="30"/>
+      <c r="AK13" s="53"/>
+      <c r="AL13" s="53"/>
       <c r="AM13" s="24" t="s">
         <v>177</v>
       </c>
@@ -9686,28 +9689,28 @@
       </c>
     </row>
     <row r="14" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="56" t="s">
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="57" t="s">
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="56" t="s">
         <v>180</v>
       </c>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
       <c r="U14" s="58"/>
       <c r="V14" s="59"/>
       <c r="W14" s="59"/>
@@ -9716,26 +9719,40 @@
       <c r="Z14" s="59"/>
       <c r="AA14" s="59"/>
       <c r="AB14" s="60"/>
-      <c r="AC14" s="57" t="s">
+      <c r="AC14" s="56" t="s">
         <v>181</v>
       </c>
-      <c r="AD14" s="57"/>
-      <c r="AE14" s="57"/>
-      <c r="AF14" s="57"/>
-      <c r="AG14" s="57"/>
-      <c r="AH14" s="57"/>
-      <c r="AI14" s="57"/>
-      <c r="AJ14" s="57"/>
-      <c r="AK14" s="38"/>
-      <c r="AL14" s="38"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="53"/>
+      <c r="AL14" s="53"/>
       <c r="AM14" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="AN14" s="25"/>
+      <c r="AN14" s="25" t="s">
+        <v>187</v>
+      </c>
       <c r="AO14" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E14:P14"/>
+    <mergeCell ref="AC14:AJ14"/>
+    <mergeCell ref="U14:AB14"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="U13:AH13"/>
+    <mergeCell ref="AI13:AJ13"/>
+    <mergeCell ref="E11:L13"/>
+    <mergeCell ref="M12:P12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="U12:AJ12"/>
     <mergeCell ref="AO9:AO10"/>
     <mergeCell ref="Q14:T14"/>
     <mergeCell ref="C11:C14"/>
@@ -9752,18 +9769,6 @@
     <mergeCell ref="U9:AB9"/>
     <mergeCell ref="AC9:AJ9"/>
     <mergeCell ref="AN9:AN10"/>
-    <mergeCell ref="E14:P14"/>
-    <mergeCell ref="AC14:AJ14"/>
-    <mergeCell ref="U14:AB14"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="U13:AH13"/>
-    <mergeCell ref="AI13:AJ13"/>
-    <mergeCell ref="E11:L13"/>
-    <mergeCell ref="M12:P12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="U12:AJ12"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eMIMO阵面数据帧格式.xlsx
+++ b/eMIMO阵面数据帧格式.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WPS_Sync\202409_eMIMO\Software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4B109C-94E5-41F5-B748-85CE2B7D229E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E062AE00-F3B4-41EF-A748-B2EC68200A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="43200" windowHeight="23445" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sub Array SPI 32bits Data Frame" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
   <si>
     <t>A15</t>
   </si>
@@ -202,12 +202,6 @@
     <t>0x2</t>
   </si>
   <si>
-    <t>phase_reg</t>
-  </si>
-  <si>
-    <t>channel_id</t>
-  </si>
-  <si>
     <t>phase</t>
   </si>
   <si>
@@ -217,10 +211,6 @@
     <t>选择移相器的8颗芯片，再对寄存器(BF,AC)和通道(0,1)进行选择，写入相位码字。</t>
   </si>
   <si>
-    <t>PS_Chip_ID表示数控移相衰减器PE44951芯片的编号，一共8个，从0计数，0至3被用于TX0至TX7通道的幅相控制、4至7被用于RX0至RX7通道的幅相控制。PS_Chip_ID=8表示全部选中；9表示选中0至3；10表示选中4至7。
-Phase_reg为0,1分别表示PE44591的BF,AC。channel_id见本页框图。</t>
-  </si>
-  <si>
     <t>0x3</t>
   </si>
   <si>
@@ -231,9 +221,6 @@
   </si>
   <si>
     <t>选择移相器的8颗芯片，再对通道(1,2)进行选择，写入7位衰减码字。</t>
-  </si>
-  <si>
-    <t>channel_id见本页框图。</t>
   </si>
   <si>
     <t>FEM_Chip_ID</t>
@@ -622,6 +609,16 @@
   </si>
   <si>
     <t>向LMK04832中写入任意数据　</t>
+  </si>
+  <si>
+    <t>Channel_ID见本页框图。</t>
+  </si>
+  <si>
+    <t>PS_Chip_ID表示数控移相衰减器PE44951芯片的编号，一共8个，从0计数，0至3被用于TX0至TX7通道的幅相控制、4至7被用于RX0至RX7通道的幅相控制。PS_Chip_ID=8表示全部选中；9表示选中0至3；10表示选中4至7。
+pha_reg_sel为0,1分别表示PE44591的BF,AC。Channel_ID见本页框图。</t>
+  </si>
+  <si>
+    <t>pha_reg_sel</t>
   </si>
 </sst>
 </file>
@@ -974,7 +971,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1049,6 +1046,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1212,8 +1212,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4820074" y="13485867"/>
-          <a:ext cx="8275578" cy="7837003"/>
+          <a:off x="4780009" y="13405737"/>
+          <a:ext cx="8191150" cy="7691787"/>
           <a:chOff x="4804172" y="13406437"/>
           <a:chExt cx="8209359" cy="7661672"/>
         </a:xfrm>
@@ -3495,8 +3495,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14365055" y="13468007"/>
-          <a:ext cx="8223059" cy="7837003"/>
+          <a:off x="14247930" y="13387877"/>
+          <a:ext cx="8234573" cy="7691787"/>
           <a:chOff x="4804172" y="13406437"/>
           <a:chExt cx="8209359" cy="7661672"/>
         </a:xfrm>
@@ -5984,6 +5984,42 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:t>）</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>请注意，这里</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>Channel_ID</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>是本表格中定义的字段，不代表物理通道。</a:t>
             </a:r>
             <a:endParaRPr lang="zh-CN" altLang="zh-CN">
               <a:effectLst/>
@@ -6397,53 +6433,53 @@
       </c>
     </row>
     <row r="18" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29" t="s">
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="31" t="s">
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="30" t="s">
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30" t="s">
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="30" t="s">
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="30"/>
-      <c r="AI18" s="30"/>
-      <c r="AJ18" s="30"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="31"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="31"/>
       <c r="AK18" s="16" t="s">
         <v>43</v>
       </c>
@@ -6456,45 +6492,45 @@
       <c r="AN18" s="22"/>
     </row>
     <row r="19" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="31" t="s">
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="30" t="s">
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30" t="s">
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
-      <c r="AC19" s="30"/>
-      <c r="AD19" s="30"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="30"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="31"/>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="31"/>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="31"/>
       <c r="AK19" s="16" t="s">
         <v>47</v>
       </c>
@@ -6509,219 +6545,219 @@
       </c>
     </row>
     <row r="20" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29" t="s">
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="30" t="s">
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="26" t="s">
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="29"/>
       <c r="AA20" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB20" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC20" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="AB20" s="11" t="s">
+      <c r="AD20" s="31"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
+      <c r="AH20" s="31"/>
+      <c r="AI20" s="31"/>
+      <c r="AJ20" s="31"/>
+      <c r="AK20" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="AC20" s="30" t="s">
+      <c r="AL20" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
-      <c r="AI20" s="30"/>
-      <c r="AJ20" s="30"/>
-      <c r="AK20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL20" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="AM20" s="10" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="AN20" s="22"/>
     </row>
     <row r="21" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="31" t="s">
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="V21" s="32"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="34"/>
       <c r="AB21" s="11" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="AC21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AD21" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE21" s="27"/>
-      <c r="AF21" s="27"/>
-      <c r="AG21" s="27"/>
-      <c r="AH21" s="27"/>
-      <c r="AI21" s="27"/>
-      <c r="AJ21" s="28"/>
+      <c r="AD21" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE21" s="28"/>
+      <c r="AF21" s="28"/>
+      <c r="AG21" s="28"/>
+      <c r="AH21" s="28"/>
+      <c r="AI21" s="28"/>
+      <c r="AJ21" s="29"/>
       <c r="AK21" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AL21" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="AN21" s="22"/>
     </row>
     <row r="22" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29" t="s">
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC22" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD22" s="28"/>
+      <c r="AE22" s="28"/>
+      <c r="AF22" s="28"/>
+      <c r="AG22" s="28"/>
+      <c r="AH22" s="28"/>
+      <c r="AI22" s="28"/>
+      <c r="AJ22" s="29"/>
+      <c r="AK22" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="30" t="s">
+      <c r="AL22" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="V22" s="27"/>
-      <c r="W22" s="27"/>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="27"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="11" t="s">
+      <c r="AM22" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="AB22" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC22" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD22" s="27"/>
-      <c r="AE22" s="27"/>
-      <c r="AF22" s="27"/>
-      <c r="AG22" s="27"/>
-      <c r="AH22" s="27"/>
-      <c r="AI22" s="27"/>
-      <c r="AJ22" s="28"/>
-      <c r="AK22" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL22" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM22" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="AN22" s="22"/>
     </row>
     <row r="23" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="31" t="s">
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="26" t="s">
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="27"/>
-      <c r="AG23" s="27"/>
-      <c r="AH23" s="27"/>
-      <c r="AI23" s="27"/>
-      <c r="AJ23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
+      <c r="AC23" s="28"/>
+      <c r="AD23" s="28"/>
+      <c r="AE23" s="28"/>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="28"/>
+      <c r="AH23" s="28"/>
+      <c r="AI23" s="28"/>
+      <c r="AJ23" s="29"/>
       <c r="AK23" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="AL23" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="AM23" s="10" t="s">
         <v>39</v>
@@ -6729,50 +6765,50 @@
       <c r="AN23" s="22"/>
     </row>
     <row r="24" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="31" t="s">
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="26" t="s">
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V24" s="27"/>
-      <c r="W24" s="27"/>
-      <c r="X24" s="27"/>
-      <c r="Y24" s="27"/>
-      <c r="Z24" s="27"/>
-      <c r="AA24" s="27"/>
-      <c r="AB24" s="27"/>
-      <c r="AC24" s="27"/>
-      <c r="AD24" s="27"/>
-      <c r="AE24" s="27"/>
-      <c r="AF24" s="27"/>
-      <c r="AG24" s="27"/>
-      <c r="AH24" s="27"/>
-      <c r="AI24" s="27"/>
-      <c r="AJ24" s="28"/>
+      <c r="V24" s="28"/>
+      <c r="W24" s="28"/>
+      <c r="X24" s="28"/>
+      <c r="Y24" s="28"/>
+      <c r="Z24" s="28"/>
+      <c r="AA24" s="28"/>
+      <c r="AB24" s="28"/>
+      <c r="AC24" s="28"/>
+      <c r="AD24" s="28"/>
+      <c r="AE24" s="28"/>
+      <c r="AF24" s="28"/>
+      <c r="AG24" s="28"/>
+      <c r="AH24" s="28"/>
+      <c r="AI24" s="28"/>
+      <c r="AJ24" s="29"/>
       <c r="AK24" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AL24" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AM24" s="10" t="s">
         <v>39</v>
@@ -6780,109 +6816,109 @@
       <c r="AN24" s="22"/>
     </row>
     <row r="25" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="31" t="s">
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="26" t="s">
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="27"/>
-      <c r="AB25" s="27"/>
-      <c r="AC25" s="30" t="s">
+      <c r="V25" s="28"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
+      <c r="AC25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="AD25" s="30"/>
-      <c r="AE25" s="30"/>
-      <c r="AF25" s="30"/>
-      <c r="AG25" s="26" t="s">
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="AH25" s="27"/>
-      <c r="AI25" s="27"/>
-      <c r="AJ25" s="28"/>
+      <c r="AH25" s="28"/>
+      <c r="AI25" s="28"/>
+      <c r="AJ25" s="29"/>
       <c r="AK25" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AL25" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AM25" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AN25" s="22"/>
     </row>
     <row r="26" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29" t="s">
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="26" t="s">
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="29"/>
       <c r="AB26" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC26" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="30"/>
+        <v>137</v>
+      </c>
+      <c r="AC26" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="31"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="31"/>
       <c r="AK26" s="16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AL26" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AM26" s="10" t="s">
         <v>39</v>
@@ -6890,54 +6926,54 @@
       <c r="AN26" s="22"/>
     </row>
     <row r="27" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="26" t="s">
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V27" s="27"/>
-      <c r="W27" s="27"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-      <c r="AA27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="29"/>
       <c r="AB27" s="11" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="AC27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AD27" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE27" s="27"/>
-      <c r="AF27" s="27"/>
-      <c r="AG27" s="27"/>
-      <c r="AH27" s="27"/>
-      <c r="AI27" s="27"/>
-      <c r="AJ27" s="28"/>
+      <c r="AD27" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE27" s="28"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="28"/>
+      <c r="AH27" s="28"/>
+      <c r="AI27" s="28"/>
+      <c r="AJ27" s="29"/>
       <c r="AK27" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AL27" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AM27" s="10" t="s">
         <v>39</v>
@@ -6945,61 +6981,61 @@
       <c r="AN27" s="22"/>
     </row>
     <row r="28" spans="4:40" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29" t="s">
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29" t="s">
+      <c r="N28" s="30"/>
+      <c r="O28" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC28" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="28"/>
+      <c r="AH28" s="28"/>
+      <c r="AI28" s="28"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL28" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="30" t="s">
+      <c r="AM28" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC28" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF28" s="27"/>
-      <c r="AG28" s="27"/>
-      <c r="AH28" s="27"/>
-      <c r="AI28" s="27"/>
-      <c r="AJ28" s="28"/>
-      <c r="AK28" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL28" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM28" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="AN28" s="22"/>
     </row>
@@ -7645,8 +7681,8 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7668,126 +7704,126 @@
   <sheetData>
     <row r="21" spans="5:44" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="P21" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="Q21" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="50" t="s">
+      <c r="R21" s="52"/>
+      <c r="S21" s="52"/>
+      <c r="T21" s="52"/>
+      <c r="U21" s="52"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="X21" s="52"/>
+      <c r="Y21" s="52"/>
+      <c r="Z21" s="52"/>
+      <c r="AA21" s="52"/>
+      <c r="AB21" s="52"/>
+      <c r="AC21" s="52"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF21" s="52"/>
+      <c r="AG21" s="52"/>
+      <c r="AH21" s="52"/>
+      <c r="AI21" s="52"/>
+      <c r="AJ21" s="52"/>
+      <c r="AK21" s="52"/>
+      <c r="AL21" s="53"/>
+      <c r="AM21" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="50" t="s">
+      <c r="AN21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P21" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q21" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="R21" s="51"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="51"/>
-      <c r="V21" s="52"/>
-      <c r="W21" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="X21" s="51"/>
-      <c r="Y21" s="51"/>
-      <c r="Z21" s="51"/>
-      <c r="AA21" s="51"/>
-      <c r="AB21" s="51"/>
-      <c r="AC21" s="51"/>
-      <c r="AD21" s="52"/>
-      <c r="AE21" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF21" s="51"/>
-      <c r="AG21" s="51"/>
-      <c r="AH21" s="51"/>
-      <c r="AI21" s="51"/>
-      <c r="AJ21" s="51"/>
-      <c r="AK21" s="51"/>
-      <c r="AL21" s="52"/>
-      <c r="AM21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AN21" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO21" s="34" t="s">
+      <c r="AO21" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="AP21" s="34" t="s">
+      <c r="AP21" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AQ21" s="34" t="s">
+      <c r="AQ21" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="AR21" s="35" t="s">
+      <c r="AR21" s="36" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="5:44" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="46"/>
+      <c r="G22" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="S22" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="U22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="V22" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>16</v>
@@ -7837,415 +7873,415 @@
       <c r="AL22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AM22" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="AN22" s="46"/>
-      <c r="AO22" s="34"/>
-      <c r="AP22" s="34"/>
-      <c r="AQ22" s="34"/>
-      <c r="AR22" s="35"/>
+      <c r="AM22" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN22" s="47"/>
+      <c r="AO22" s="35"/>
+      <c r="AP22" s="35"/>
+      <c r="AQ22" s="35"/>
+      <c r="AR22" s="36"/>
     </row>
     <row r="23" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E23" s="53" t="s">
+      <c r="E23" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
+      <c r="AH23" s="31"/>
+      <c r="AI23" s="31"/>
+      <c r="AJ23" s="31"/>
+      <c r="AK23" s="31"/>
+      <c r="AL23" s="31"/>
+      <c r="AM23" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN23" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="AO23" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="AP23" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="30"/>
-      <c r="AL23" s="30"/>
-      <c r="AM23" s="4" t="s">
+      <c r="AQ23" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="AN23" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO23" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP23" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AQ23" s="16" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="24" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="36" t="s">
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="36" t="s">
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="26" t="s">
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="26" t="s">
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="30" t="s">
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="30"/>
-      <c r="AD24" s="30"/>
-      <c r="AE24" s="30"/>
-      <c r="AF24" s="30"/>
-      <c r="AG24" s="30"/>
-      <c r="AH24" s="30"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="30"/>
-      <c r="AK24" s="30"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="31"/>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="31"/>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
+      <c r="AH24" s="31"/>
+      <c r="AI24" s="31"/>
+      <c r="AJ24" s="31"/>
+      <c r="AK24" s="31"/>
       <c r="AL24" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="AM24" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="AN24" s="47" t="s">
-        <v>122</v>
+      <c r="AM24" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN24" s="48" t="s">
+        <v>118</v>
       </c>
       <c r="AO24" s="16" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AP24" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="AQ24" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="26" t="s">
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="26" t="s">
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="26" t="s">
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="27"/>
-      <c r="AB25" s="27"/>
-      <c r="AC25" s="27"/>
-      <c r="AD25" s="27"/>
-      <c r="AE25" s="27"/>
-      <c r="AF25" s="27"/>
-      <c r="AG25" s="27"/>
-      <c r="AH25" s="27"/>
-      <c r="AI25" s="27"/>
-      <c r="AJ25" s="27"/>
-      <c r="AK25" s="27"/>
-      <c r="AL25" s="28"/>
-      <c r="AM25" s="48"/>
-      <c r="AN25" s="48"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
+      <c r="AC25" s="28"/>
+      <c r="AD25" s="28"/>
+      <c r="AE25" s="28"/>
+      <c r="AF25" s="28"/>
+      <c r="AG25" s="28"/>
+      <c r="AH25" s="28"/>
+      <c r="AI25" s="28"/>
+      <c r="AJ25" s="28"/>
+      <c r="AK25" s="28"/>
+      <c r="AL25" s="29"/>
+      <c r="AM25" s="49"/>
+      <c r="AN25" s="49"/>
       <c r="AO25" s="16" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AP25" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="AQ25" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="26" t="s">
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+      <c r="AC26" s="28"/>
+      <c r="AD26" s="28"/>
+      <c r="AE26" s="28"/>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="28"/>
+      <c r="AH26" s="28"/>
+      <c r="AI26" s="28"/>
+      <c r="AJ26" s="28"/>
+      <c r="AK26" s="28"/>
+      <c r="AL26" s="29"/>
+      <c r="AM26" s="49"/>
+      <c r="AN26" s="49"/>
+      <c r="AO26" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP26" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ26" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR26" s="17" t="s">
         <v>132</v>
-      </c>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
-      <c r="AC26" s="27"/>
-      <c r="AD26" s="27"/>
-      <c r="AE26" s="27"/>
-      <c r="AF26" s="27"/>
-      <c r="AG26" s="27"/>
-      <c r="AH26" s="27"/>
-      <c r="AI26" s="27"/>
-      <c r="AJ26" s="27"/>
-      <c r="AK26" s="27"/>
-      <c r="AL26" s="28"/>
-      <c r="AM26" s="48"/>
-      <c r="AN26" s="48"/>
-      <c r="AO26" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="AP26" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="AQ26" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="AR26" s="17" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="27" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="26" t="s">
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="26" t="s">
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-      <c r="AA27" s="27"/>
-      <c r="AB27" s="27"/>
-      <c r="AC27" s="27"/>
-      <c r="AD27" s="28"/>
-      <c r="AE27" s="30" t="s">
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30" t="s">
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="31"/>
+      <c r="AH27" s="31"/>
+      <c r="AI27" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="30"/>
-      <c r="AM27" s="48"/>
-      <c r="AN27" s="48"/>
+      <c r="AJ27" s="31"/>
+      <c r="AK27" s="31"/>
+      <c r="AL27" s="31"/>
+      <c r="AM27" s="49"/>
+      <c r="AN27" s="49"/>
       <c r="AO27" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AP27" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="AQ27" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="26" t="s">
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="29"/>
       <c r="AD28" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE28" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF28" s="27"/>
-      <c r="AG28" s="27"/>
-      <c r="AH28" s="27"/>
-      <c r="AI28" s="27"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="27"/>
-      <c r="AL28" s="28"/>
-      <c r="AM28" s="48"/>
-      <c r="AN28" s="48"/>
+        <v>137</v>
+      </c>
+      <c r="AE28" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="28"/>
+      <c r="AH28" s="28"/>
+      <c r="AI28" s="28"/>
+      <c r="AJ28" s="28"/>
+      <c r="AK28" s="28"/>
+      <c r="AL28" s="29"/>
+      <c r="AM28" s="49"/>
+      <c r="AN28" s="49"/>
       <c r="AO28" s="16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AP28" s="10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AQ28" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="5:44" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="26" t="s">
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="29"/>
       <c r="AD29" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AE29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AF29" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG29" s="27"/>
-      <c r="AH29" s="27"/>
-      <c r="AI29" s="27"/>
-      <c r="AJ29" s="27"/>
-      <c r="AK29" s="27"/>
-      <c r="AL29" s="28"/>
-      <c r="AM29" s="49"/>
-      <c r="AN29" s="49"/>
+      <c r="AF29" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG29" s="28"/>
+      <c r="AH29" s="28"/>
+      <c r="AI29" s="28"/>
+      <c r="AJ29" s="28"/>
+      <c r="AK29" s="28"/>
+      <c r="AL29" s="29"/>
+      <c r="AM29" s="50"/>
+      <c r="AN29" s="50"/>
       <c r="AO29" s="16" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AP29" s="10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AQ29" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -8310,117 +8346,117 @@
   <sheetData>
     <row r="13" spans="3:39" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="O13" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="N13" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="V13" s="51"/>
-      <c r="W13" s="51"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="51"/>
-      <c r="AA13" s="51"/>
-      <c r="AB13" s="52"/>
-      <c r="AC13" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD13" s="51"/>
-      <c r="AE13" s="51"/>
-      <c r="AF13" s="51"/>
-      <c r="AG13" s="51"/>
-      <c r="AH13" s="51"/>
-      <c r="AI13" s="51"/>
-      <c r="AJ13" s="52"/>
-      <c r="AK13" s="54" t="s">
+      <c r="P13" s="52"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="V13" s="52"/>
+      <c r="W13" s="52"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="52"/>
+      <c r="AA13" s="52"/>
+      <c r="AB13" s="53"/>
+      <c r="AC13" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD13" s="52"/>
+      <c r="AE13" s="52"/>
+      <c r="AF13" s="52"/>
+      <c r="AG13" s="52"/>
+      <c r="AH13" s="52"/>
+      <c r="AI13" s="52"/>
+      <c r="AJ13" s="53"/>
+      <c r="AK13" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="AL13" s="34" t="s">
+      <c r="AL13" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AM13" s="34" t="s">
+      <c r="AM13" s="35" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="3:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="46"/>
+      <c r="E14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
@@ -8470,307 +8506,307 @@
       <c r="AJ14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AK14" s="55"/>
-      <c r="AL14" s="34"/>
-      <c r="AM14" s="34"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="35"/>
+      <c r="AM14" s="35"/>
     </row>
     <row r="15" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="29" t="s">
+      <c r="C15" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="28" t="s">
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="30"/>
-      <c r="K15" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="L15" s="33"/>
-      <c r="M15" s="31" t="s">
+      <c r="J15" s="31"/>
+      <c r="K15" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" s="34"/>
+      <c r="M15" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="26" t="s">
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="27"/>
-      <c r="Z15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="29"/>
       <c r="AA15" s="11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AB15" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC15" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AD15" s="27"/>
-      <c r="AE15" s="27"/>
-      <c r="AF15" s="27"/>
-      <c r="AG15" s="27"/>
-      <c r="AH15" s="27"/>
-      <c r="AI15" s="27"/>
-      <c r="AJ15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="29"/>
       <c r="AK15" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AL15" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="32" t="s">
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="31" t="s">
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="26" t="s">
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="27"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="27"/>
-      <c r="AB16" s="27"/>
-      <c r="AC16" s="27"/>
-      <c r="AD16" s="27"/>
-      <c r="AE16" s="27"/>
-      <c r="AF16" s="27"/>
-      <c r="AG16" s="27"/>
-      <c r="AH16" s="27"/>
-      <c r="AI16" s="27"/>
-      <c r="AJ16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="28"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="28"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28"/>
+      <c r="AH16" s="28"/>
+      <c r="AI16" s="28"/>
+      <c r="AJ16" s="29"/>
       <c r="AK16" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AL16" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AM16" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="32" t="s">
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="31" t="s">
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="26" t="s">
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="27"/>
-      <c r="Y17" s="27"/>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="27"/>
-      <c r="AB17" s="27"/>
-      <c r="AC17" s="27"/>
-      <c r="AD17" s="27"/>
-      <c r="AE17" s="27"/>
-      <c r="AF17" s="28"/>
-      <c r="AG17" s="26" t="s">
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="29"/>
+      <c r="AG17" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="AH17" s="27"/>
-      <c r="AI17" s="27"/>
-      <c r="AJ17" s="28"/>
+      <c r="AH17" s="28"/>
+      <c r="AI17" s="28"/>
+      <c r="AJ17" s="29"/>
       <c r="AK17" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AL17" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="28" t="s">
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="30"/>
-      <c r="K18" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="L18" s="33"/>
-      <c r="M18" s="29" t="s">
+      <c r="J18" s="31"/>
+      <c r="K18" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L18" s="34"/>
+      <c r="M18" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V18" s="28"/>
+      <c r="W18" s="28"/>
+      <c r="X18" s="28"/>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28"/>
+      <c r="AH18" s="28"/>
+      <c r="AI18" s="28"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="AL18" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM18" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
-      <c r="X18" s="27"/>
-      <c r="Y18" s="27"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF18" s="27"/>
-      <c r="AG18" s="27"/>
-      <c r="AH18" s="27"/>
-      <c r="AI18" s="27"/>
-      <c r="AJ18" s="28"/>
-      <c r="AK18" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="AL18" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AM18" s="10" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="19" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="28" t="s">
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="30"/>
-      <c r="K19" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="L19" s="33"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L19" s="34"/>
       <c r="M19" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="31" t="s">
+      <c r="N19" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="O19" s="33"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC19" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD19" s="31"/>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK19" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="O19" s="32"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="30" t="s">
+      <c r="AL19" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="5" t="s">
+      <c r="AM19" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="AC19" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD19" s="30"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="AK19" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL19" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="AM19" s="10" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -8836,117 +8872,117 @@
   <sheetData>
     <row r="13" spans="3:39" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="O13" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="N13" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="V13" s="51"/>
-      <c r="W13" s="51"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="51"/>
-      <c r="AA13" s="51"/>
-      <c r="AB13" s="52"/>
-      <c r="AC13" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD13" s="51"/>
-      <c r="AE13" s="51"/>
-      <c r="AF13" s="51"/>
-      <c r="AG13" s="51"/>
-      <c r="AH13" s="51"/>
-      <c r="AI13" s="51"/>
-      <c r="AJ13" s="52"/>
-      <c r="AK13" s="54" t="s">
+      <c r="P13" s="52"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="V13" s="52"/>
+      <c r="W13" s="52"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="52"/>
+      <c r="AA13" s="52"/>
+      <c r="AB13" s="53"/>
+      <c r="AC13" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD13" s="52"/>
+      <c r="AE13" s="52"/>
+      <c r="AF13" s="52"/>
+      <c r="AG13" s="52"/>
+      <c r="AH13" s="52"/>
+      <c r="AI13" s="52"/>
+      <c r="AJ13" s="53"/>
+      <c r="AK13" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="AL13" s="34" t="s">
+      <c r="AL13" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AM13" s="34" t="s">
+      <c r="AM13" s="35" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="3:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="46"/>
+      <c r="E14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
@@ -8996,293 +9032,293 @@
       <c r="AJ14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AK14" s="55"/>
-      <c r="AL14" s="34"/>
-      <c r="AM14" s="34"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="35"/>
+      <c r="AM14" s="35"/>
     </row>
     <row r="15" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="36" t="s">
+      <c r="C15" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="31" t="s">
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="26" t="s">
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="27"/>
-      <c r="Z15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="29"/>
       <c r="AA15" s="11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AB15" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC15" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AD15" s="27"/>
-      <c r="AE15" s="27"/>
-      <c r="AF15" s="27"/>
-      <c r="AG15" s="27"/>
-      <c r="AH15" s="27"/>
-      <c r="AI15" s="27"/>
-      <c r="AJ15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="29"/>
       <c r="AK15" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AL15" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="31" t="s">
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="26" t="s">
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="27"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="27"/>
-      <c r="AB16" s="27"/>
-      <c r="AC16" s="27"/>
-      <c r="AD16" s="27"/>
-      <c r="AE16" s="27"/>
-      <c r="AF16" s="27"/>
-      <c r="AG16" s="27"/>
-      <c r="AH16" s="27"/>
-      <c r="AI16" s="27"/>
-      <c r="AJ16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="28"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="28"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28"/>
+      <c r="AH16" s="28"/>
+      <c r="AI16" s="28"/>
+      <c r="AJ16" s="29"/>
       <c r="AK16" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AL16" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AM16" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="31" t="s">
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="26" t="s">
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="27"/>
-      <c r="Y17" s="27"/>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="27"/>
-      <c r="AB17" s="28"/>
-      <c r="AC17" s="30" t="s">
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="29"/>
+      <c r="AC17" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AD17" s="30"/>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
-      <c r="AH17" s="30"/>
-      <c r="AI17" s="30"/>
-      <c r="AJ17" s="30"/>
+      <c r="AD17" s="31"/>
+      <c r="AE17" s="31"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="31"/>
+      <c r="AH17" s="31"/>
+      <c r="AI17" s="31"/>
+      <c r="AJ17" s="31"/>
       <c r="AK17" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AL17" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="41"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="42"/>
       <c r="M18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="O18" s="32"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="26" t="s">
+      <c r="N18" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="O18" s="33"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
-      <c r="X18" s="27"/>
-      <c r="Y18" s="27"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="30" t="s">
+      <c r="V18" s="28"/>
+      <c r="W18" s="28"/>
+      <c r="X18" s="28"/>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF18" s="27"/>
-      <c r="AG18" s="27"/>
-      <c r="AH18" s="27"/>
-      <c r="AI18" s="27"/>
-      <c r="AJ18" s="28"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28"/>
+      <c r="AH18" s="28"/>
+      <c r="AI18" s="28"/>
+      <c r="AJ18" s="29"/>
       <c r="AK18" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AL18" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="3:39" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="29" t="s">
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="N19" s="29"/>
-      <c r="O19" s="32" t="s">
+      <c r="N19" s="30"/>
+      <c r="O19" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC19" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD19" s="31"/>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK19" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="30" t="s">
+      <c r="AL19" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AC19" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD19" s="30"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="AK19" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL19" s="10" t="s">
-        <v>162</v>
-      </c>
       <c r="AM19" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -9341,123 +9377,123 @@
   <sheetData>
     <row r="9" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="N9" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="O9" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="53"/>
+      <c r="U9" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="52"/>
+      <c r="AB9" s="53"/>
+      <c r="AC9" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="52"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="52"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="53"/>
+      <c r="AK9" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="50" t="s">
+      <c r="AL9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="N9" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="52"/>
-      <c r="U9" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="52"/>
-      <c r="AC9" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="51"/>
-      <c r="AI9" s="51"/>
-      <c r="AJ9" s="52"/>
-      <c r="AK9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM9" s="54" t="s">
+      <c r="AM9" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="AN9" s="34" t="s">
+      <c r="AN9" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AO9" s="34" t="s">
+      <c r="AO9" s="35" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="3:41" x14ac:dyDescent="0.2">
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="46"/>
+      <c r="E10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="Q10" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>16</v>
@@ -9507,235 +9543,235 @@
       <c r="AJ10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AK10" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL10" s="46"/>
-      <c r="AM10" s="55"/>
-      <c r="AN10" s="34"/>
-      <c r="AO10" s="34"/>
+      <c r="AK10" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL10" s="47"/>
+      <c r="AM10" s="56"/>
+      <c r="AN10" s="35"/>
+      <c r="AO10" s="35"/>
     </row>
     <row r="11" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="57" t="s">
+        <v>174</v>
+      </c>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK11" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="AL11" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="31" t="s">
+      <c r="AM11" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AO11" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="56" t="s">
-        <v>178</v>
-      </c>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="30"/>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="AK11" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="AL11" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM11" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AN11" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO11" s="10" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="12" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="N12" s="32"/>
-      <c r="O12" s="32"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="30" t="s">
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="V12" s="27"/>
-      <c r="W12" s="27"/>
-      <c r="X12" s="27"/>
-      <c r="Y12" s="27"/>
-      <c r="Z12" s="27"/>
-      <c r="AA12" s="27"/>
-      <c r="AB12" s="27"/>
-      <c r="AC12" s="27"/>
-      <c r="AD12" s="27"/>
-      <c r="AE12" s="27"/>
-      <c r="AF12" s="27"/>
-      <c r="AG12" s="27"/>
-      <c r="AH12" s="27"/>
-      <c r="AI12" s="27"/>
-      <c r="AJ12" s="28"/>
-      <c r="AK12" s="53"/>
-      <c r="AL12" s="53"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="59" t="s">
+        <v>174</v>
+      </c>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="28"/>
+      <c r="AH12" s="28"/>
+      <c r="AI12" s="28"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="54"/>
+      <c r="AL12" s="54"/>
       <c r="AM12" s="24" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AN12" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AO12" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="56" t="s">
-        <v>175</v>
-      </c>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="27"/>
-      <c r="AG13" s="27"/>
-      <c r="AH13" s="28"/>
-      <c r="AI13" s="56" t="s">
-        <v>184</v>
-      </c>
-      <c r="AJ13" s="30"/>
-      <c r="AK13" s="53"/>
-      <c r="AL13" s="53"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="59" t="s">
+        <v>174</v>
+      </c>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="28"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="54"/>
+      <c r="AL13" s="54"/>
       <c r="AM13" s="24" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AN13" s="25" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AO13" s="25" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="3:41" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="56" t="s">
-        <v>180</v>
-      </c>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="58"/>
-      <c r="V14" s="59"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="59"/>
-      <c r="Y14" s="59"/>
-      <c r="Z14" s="59"/>
-      <c r="AA14" s="59"/>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="AD14" s="56"/>
-      <c r="AE14" s="56"/>
-      <c r="AF14" s="56"/>
-      <c r="AG14" s="56"/>
-      <c r="AH14" s="56"/>
-      <c r="AI14" s="56"/>
-      <c r="AJ14" s="56"/>
-      <c r="AK14" s="53"/>
-      <c r="AL14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="57" t="s">
+        <v>176</v>
+      </c>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="59"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="60"/>
+      <c r="Z14" s="60"/>
+      <c r="AA14" s="60"/>
+      <c r="AB14" s="61"/>
+      <c r="AC14" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD14" s="57"/>
+      <c r="AE14" s="57"/>
+      <c r="AF14" s="57"/>
+      <c r="AG14" s="57"/>
+      <c r="AH14" s="57"/>
+      <c r="AI14" s="57"/>
+      <c r="AJ14" s="57"/>
+      <c r="AK14" s="54"/>
+      <c r="AL14" s="54"/>
       <c r="AM14" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="AN14" s="25" t="s">
         <v>183</v>
-      </c>
-      <c r="AN14" s="25" t="s">
-        <v>187</v>
       </c>
       <c r="AO14" s="25"/>
     </row>
